--- a/artfynd/A 48369-2023 artfynd.xlsx
+++ b/artfynd/A 48369-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113161656</v>
+        <v>113161654</v>
       </c>
       <c r="B2" t="n">
-        <v>56910</v>
+        <v>90009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634940</v>
+        <v>634836</v>
       </c>
       <c r="R2" t="n">
-        <v>7087373</v>
+        <v>7087413</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113161654</v>
+        <v>113161656</v>
       </c>
       <c r="B3" t="n">
-        <v>89993</v>
+        <v>56910</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634836</v>
+        <v>634940</v>
       </c>
       <c r="R3" t="n">
-        <v>7087413</v>
+        <v>7087373</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 48369-2023 artfynd.xlsx
+++ b/artfynd/A 48369-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113161654</v>
+        <v>113161656</v>
       </c>
       <c r="B2" t="n">
-        <v>90009</v>
+        <v>56911</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634836</v>
+        <v>634940</v>
       </c>
       <c r="R2" t="n">
-        <v>7087413</v>
+        <v>7087373</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113161656</v>
+        <v>113161654</v>
       </c>
       <c r="B3" t="n">
-        <v>56910</v>
+        <v>90021</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634940</v>
+        <v>634836</v>
       </c>
       <c r="R3" t="n">
-        <v>7087373</v>
+        <v>7087413</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 48369-2023 artfynd.xlsx
+++ b/artfynd/A 48369-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113161656</v>
+        <v>113161654</v>
       </c>
       <c r="B2" t="n">
-        <v>56911</v>
+        <v>90043</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634940</v>
+        <v>634836</v>
       </c>
       <c r="R2" t="n">
-        <v>7087373</v>
+        <v>7087413</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113161654</v>
+        <v>113161656</v>
       </c>
       <c r="B3" t="n">
-        <v>90021</v>
+        <v>56911</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634836</v>
+        <v>634940</v>
       </c>
       <c r="R3" t="n">
-        <v>7087413</v>
+        <v>7087373</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 48369-2023 artfynd.xlsx
+++ b/artfynd/A 48369-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113161654</v>
+        <v>113161656</v>
       </c>
       <c r="B2" t="n">
-        <v>90043</v>
+        <v>56914</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634836</v>
+        <v>634940</v>
       </c>
       <c r="R2" t="n">
-        <v>7087413</v>
+        <v>7087373</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113161656</v>
+        <v>113161654</v>
       </c>
       <c r="B3" t="n">
-        <v>56911</v>
+        <v>90047</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634940</v>
+        <v>634836</v>
       </c>
       <c r="R3" t="n">
-        <v>7087373</v>
+        <v>7087413</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 48369-2023 artfynd.xlsx
+++ b/artfynd/A 48369-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48369-2023 artfynd.xlsx
+++ b/artfynd/A 48369-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1816,6 +1816,412 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128423175</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>635169</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7087269</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128423121</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>635167</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7087269</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128428566</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>634515</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7087381</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128428553</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>634490</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7087432</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Långt ned på gran</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48369-2023 artfynd.xlsx
+++ b/artfynd/A 48369-2023 artfynd.xlsx
@@ -1821,7 +1821,7 @@
         <v>128423175</v>
       </c>
       <c r="B13" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>128423121</v>
       </c>
       <c r="B14" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>128428566</v>
       </c>
       <c r="B15" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>128428553</v>
       </c>
       <c r="B16" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 48369-2023 artfynd.xlsx
+++ b/artfynd/A 48369-2023 artfynd.xlsx
@@ -1821,7 +1821,7 @@
         <v>128423175</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>128423121</v>
       </c>
       <c r="B14" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>128428566</v>
       </c>
       <c r="B15" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>128428553</v>
       </c>
       <c r="B16" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 48369-2023 artfynd.xlsx
+++ b/artfynd/A 48369-2023 artfynd.xlsx
@@ -1821,7 +1821,7 @@
         <v>128423175</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 48369-2023 artfynd.xlsx
+++ b/artfynd/A 48369-2023 artfynd.xlsx
@@ -2010,7 +2010,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 48369-2023 artfynd.xlsx
+++ b/artfynd/A 48369-2023 artfynd.xlsx
@@ -2010,7 +2010,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Amanda Portström, Isac Enetjärn, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 48369-2023 artfynd.xlsx
+++ b/artfynd/A 48369-2023 artfynd.xlsx
@@ -1821,7 +1821,7 @@
         <v>128423175</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>128423121</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>128428566</v>
       </c>
       <c r="B15" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>128428553</v>
       </c>
       <c r="B16" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 48369-2023 artfynd.xlsx
+++ b/artfynd/A 48369-2023 artfynd.xlsx
@@ -1821,7 +1821,7 @@
         <v>128423175</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 48369-2023 artfynd.xlsx
+++ b/artfynd/A 48369-2023 artfynd.xlsx
@@ -1821,7 +1821,7 @@
         <v>128423175</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>128423121</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>128428566</v>
       </c>
       <c r="B15" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>128428553</v>
       </c>
       <c r="B16" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 48369-2023 artfynd.xlsx
+++ b/artfynd/A 48369-2023 artfynd.xlsx
@@ -1821,7 +1821,7 @@
         <v>128423175</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>128423121</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>128428566</v>
       </c>
       <c r="B15" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>128428553</v>
       </c>
       <c r="B16" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 48369-2023 artfynd.xlsx
+++ b/artfynd/A 48369-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113161656</v>
+        <v>128423112</v>
       </c>
       <c r="B2" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634940</v>
+        <v>634544</v>
       </c>
       <c r="R2" t="n">
-        <v>7087373</v>
+        <v>7087320</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,49 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113161654</v>
+        <v>128428595</v>
       </c>
       <c r="B3" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634836</v>
+        <v>634678</v>
       </c>
       <c r="R3" t="n">
-        <v>7087414</v>
+        <v>7087320</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119253467</v>
+        <v>113161653</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635068</v>
+        <v>634738</v>
       </c>
       <c r="R4" t="n">
-        <v>7087304</v>
+        <v>7087351</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +959,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emil Larsson, Julia Pettersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119258760</v>
+        <v>119253475</v>
       </c>
       <c r="B5" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>634793</v>
+        <v>634951</v>
       </c>
       <c r="R5" t="n">
-        <v>7087384</v>
+        <v>7087353</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,31 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Julia Pettersson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Emil Larsson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119258757</v>
+        <v>119253481</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635187</v>
+        <v>634658</v>
       </c>
       <c r="R6" t="n">
-        <v>7087281</v>
+        <v>7087354</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,31 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Julia Pettersson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Emil Larsson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119253474</v>
+        <v>119253484</v>
       </c>
       <c r="B7" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4412</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634960</v>
+        <v>634591</v>
       </c>
       <c r="R7" t="n">
-        <v>7087356</v>
+        <v>7087315</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119258733</v>
+        <v>119258763</v>
       </c>
       <c r="B8" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1316,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4412</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1340,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>635206</v>
+        <v>634713</v>
       </c>
       <c r="R8" t="n">
-        <v>7087247</v>
+        <v>7087373</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,37 +1358,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119258740</v>
+        <v>128423625</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1446,10 +1393,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>634963</v>
+        <v>634494</v>
       </c>
       <c r="R9" t="n">
-        <v>7087345</v>
+        <v>7087408</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,12 +1423,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,31 +1443,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Julia Pettersson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119253475</v>
+        <v>128428589</v>
       </c>
       <c r="B10" t="n">
-        <v>86878</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>634951</v>
+        <v>634679</v>
       </c>
       <c r="R10" t="n">
-        <v>7087353</v>
+        <v>7087311</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,12 +1520,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,27 +1540,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emil Larsson, Julia Pettersson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119253468</v>
+        <v>128428590</v>
       </c>
       <c r="B11" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,21 +1563,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4412</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635021</v>
+        <v>634658</v>
       </c>
       <c r="R11" t="n">
-        <v>7087328</v>
+        <v>7087313</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,12 +1617,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1704,27 +1637,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emil Larsson, Julia Pettersson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119253477</v>
+        <v>128423098</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1732,21 +1660,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1756,10 +1684,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>634888</v>
+        <v>635186</v>
       </c>
       <c r="R12" t="n">
-        <v>7087401</v>
+        <v>7087317</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1786,12 +1714,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1806,22 +1734,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil Larsson, Julia Pettersson</t>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128423175</v>
+        <v>119253482</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1829,21 +1757,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1781,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>635169</v>
+        <v>634650</v>
       </c>
       <c r="R13" t="n">
-        <v>7087269</v>
+        <v>7087344</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,12 +1811,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1903,22 +1831,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+          <t>Emil Larsson, Julia Pettersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128423121</v>
+        <v>119258760</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,21 +1854,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1950,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635167</v>
+        <v>634793</v>
       </c>
       <c r="R14" t="n">
-        <v>7087269</v>
+        <v>7087384</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1980,17 +1908,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2005,44 +1928,48 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Julia Pettersson, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128428566</v>
+        <v>128428583</v>
       </c>
       <c r="B15" t="n">
-        <v>58093</v>
+        <v>83173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +1979,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>634515</v>
+        <v>634880</v>
       </c>
       <c r="R15" t="n">
-        <v>7087381</v>
+        <v>7087375</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,53 +2041,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128428553</v>
+        <v>128423099</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>92632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hästryggen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634490</v>
+        <v>634570</v>
       </c>
       <c r="R16" t="n">
-        <v>7087432</v>
+        <v>7087303</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2195,11 +2114,6 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Långt ned på gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2212,15 +2126,4300 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128428533</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>634621</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7087294</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Isac Enetjärn</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Isac Enetjärn</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128423590</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>635182</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7087227</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>119253464</v>
+      </c>
+      <c r="B19" t="n">
+        <v>89156</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>635158</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7087220</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>119253468</v>
+      </c>
+      <c r="B20" t="n">
+        <v>89156</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>635021</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7087328</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>119253471</v>
+      </c>
+      <c r="B21" t="n">
+        <v>89156</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>635021</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7087338</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>119253473</v>
+      </c>
+      <c r="B22" t="n">
+        <v>89156</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>635009</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7087356</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>119253474</v>
+      </c>
+      <c r="B23" t="n">
+        <v>89156</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>634960</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7087356</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>119258733</v>
+      </c>
+      <c r="B24" t="n">
+        <v>89156</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>635206</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7087247</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Julia Pettersson, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>113161654</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>634836</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7087414</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>119253469</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>635021</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7087338</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>119253476</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>634875</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7087375</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>119253479</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>634696</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7087361</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>119253483</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>634591</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7087315</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128411934</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>634525</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7087336</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128428529</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>634593</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7087306</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>113161652</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>634636</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7087309</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>119253459</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>635200</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7087219</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>119253467</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>635068</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7087304</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>119253477</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>634888</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7087401</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128407951</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hästryggen, Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>635217</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7087316</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128423163</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>634542</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7087338</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128423173</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>635138</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7087339</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128423175</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>635169</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7087269</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>634969</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7087325</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128428573</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>634610</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7087361</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128428574</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>635129</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7087323</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128428578</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>634686</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7087331</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128428579</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>634645</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7087310</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>113161650</v>
+      </c>
+      <c r="B45" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>634664</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7087310</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>119258740</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>634963</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7087345</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Julia Pettersson, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128428544</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>635039</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7087283</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128428550</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>634487</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7087401</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128428552</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>635170</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7087231</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128428553</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>634490</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7087432</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Långt ned på gran</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>113161657</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>634964</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7087366</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128423121</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>635167</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7087269</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, Isac Enetjärn, Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128428534</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>634959</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7087327</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128428536</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>634669</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7087314</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>119253478</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>634838</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7087383</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128428566</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>634515</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7087381</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>113161656</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>634940</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7087373</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128423588</v>
+      </c>
+      <c r="B58" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>634560</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7087311</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>119258754</v>
+      </c>
+      <c r="B59" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hästryggen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>635193</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7087318</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Julia Pettersson, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48369-2023 artfynd.xlsx
+++ b/artfynd/A 48369-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423112</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428595</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161653</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253475</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253481</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253484</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258763</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423625</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428589</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428590</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423098</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253482</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258760</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2038,6 +2108,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428583</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2135,6 +2210,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423099</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2232,6 +2312,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428533</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2329,6 +2414,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423590</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2426,6 +2516,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253464</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2523,6 +2618,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253468</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2620,6 +2720,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253471</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2717,6 +2822,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253473</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2814,6 +2924,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253474</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2915,6 +3030,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258733</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3012,6 +3132,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161654</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3109,6 +3234,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253469</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3206,6 +3336,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253476</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3303,6 +3438,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253479</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3400,6 +3540,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253483</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3507,6 +3652,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128411934</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3604,6 +3754,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428529</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3701,6 +3856,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161652</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3798,6 +3958,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253459</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3895,6 +4060,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253467</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3992,6 +4162,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253477</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4099,6 +4274,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128407951</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4196,6 +4376,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423163</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4293,6 +4478,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423173</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4390,6 +4580,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423175</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4487,6 +4682,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428572</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4584,6 +4784,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428573</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4681,6 +4886,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428574</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4778,6 +4988,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428578</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4875,6 +5090,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428579</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4972,6 +5192,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161650</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5073,6 +5298,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258740</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5170,6 +5400,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428544</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5275,6 +5510,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428550</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5380,6 +5620,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428552</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5490,6 +5735,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428553</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5592,6 +5842,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161657</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5694,6 +5949,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423121</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5804,6 +6064,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428534</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5914,6 +6179,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428536</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6023,6 +6293,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253478</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6120,6 +6395,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428566</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6222,6 +6502,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161656</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6319,6 +6604,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423588</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6420,8 +6710,73 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258754</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>